--- a/out/Attention-Mamba1_repeat_1_000001.xlsx
+++ b/out/Attention-Mamba1_repeat_1_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.0804624974787482</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.0804624974787482</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.5195375025212517</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.5195375025212517</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.5195375025212517</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.5195375025212517</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.5195375025212517</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.5195375025212517</v>
+        <v>-0.4694694960034206</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.5195375025212517</v>
+        <v>-0.4694694960034206</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.0804624974787482</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.0804624974787482</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.0804624974787482</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.0804624974787482</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.0804624974787482</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.0804624974787482</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.0804624974787482</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.0804624974787482</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.0804624974787482</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.0804624974787482</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.0804624974787482</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.0804624974787482</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.0804624974787482</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.0804624974787482</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.0804624974787482</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.0804624974787482</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.0804624974787482</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.0804624974787482</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.0804624974787482</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.0804624974787482</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.0804624974787482</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.0804624974787482</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-0.4694694960034206</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-0.4694694960034206</v>
       </c>
       <c r="JC43" t="n">
-        <v>-9.342816364043393e-05</v>
+        <v>-6.16557790839579e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.04022734760312981</v>
+        <v>0.02654718836505428</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.08056226633211667</v>
+        <v>0.05316522415700695</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1554195181548552</v>
+        <v>0.1025650008440343</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.3512782694338442</v>
+        <v>0.2318175818085629</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.04780842403324903</v>
+        <v>0.0315495692094549</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-9.227858435864231</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2912771945012859</v>
+        <v>0.1922212430598307</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.009700684866417434</v>
+        <v>0.006401087904233836</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-9.227858435864231</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2627953484839797</v>
+        <v>0.1734242346915815</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.008400144827556133</v>
+        <v>0.00554210920987265</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-9.227858435864231</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2698856671275217</v>
+        <v>0.1781017033430846</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.004104104061585137</v>
+        <v>0.002706868677100651</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.2696850453942199</v>
+        <v>0.1779676101855426</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.001956083678599633</v>
+        <v>0.001289248410714647</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2694887422620926</v>
+        <v>0.1778363776789356</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0008122505780637044</v>
+        <v>0.0005338954765433691</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.5195375025212517</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.2691542393066245</v>
+        <v>0.1776139916552119</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0005614068736791735</v>
+        <v>0.000368489001172643</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.5195375025212517</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.2694640624969266</v>
+        <v>0.1778168014580135</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0002314533376848248</v>
+        <v>0.0001509174597267782</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.5195375025212517</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.2693649465762211</v>
+        <v>0.1777496138310996</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001172754048326176</v>
+        <v>7.584876494397121e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.5195375025212517</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2693684664920014</v>
+        <v>0.1777502553198044</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>4.328749595342138e-05</v>
+        <v>2.701670927346418e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.5195375025212517</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.2693369532375331</v>
+        <v>0.1777276758793415</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>2.134113002145089e-05</v>
+        <v>1.217899784007667e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.5195375025212517</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.2693362941468426</v>
+        <v>0.1777255547337187</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>7.987449840330433e-06</v>
+        <v>3.470075982824195e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.5195375025212517</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.269330898129083</v>
+        <v>0.1777202884901725</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>8.610817715762575e-07</v>
+        <v>-7.373950752172664e-07</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.2693251511735464</v>
+        <v>0.1777147684384205</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-2.232968880383854e-06</v>
+        <v>-3.155312586922569e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.2693192833855918</v>
+        <v>0.1777091899131176</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-3.759791964848896e-06</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.2693139931434903</v>
+        <v>0.1777039964183834</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2693087052046398</v>
+        <v>0.1776988041326664</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.817481666896968e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2693034333705888</v>
+        <v>0.1776986686240607</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.2693034732260611</v>
+        <v>0.177698708479533</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2693035130815334</v>
+        <v>0.1776987483350053</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2693035051104389</v>
+        <v>0.1776987403639108</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.269303664532328</v>
+        <v>0.1776988997857999</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2693035688791945</v>
+        <v>0.1776988041326664</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2693039196073508</v>
+        <v>0.1776991548608227</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2693036725034225</v>
+        <v>0.1776989077568944</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2693036326479502</v>
+        <v>0.1776988679014221</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2693035688791945</v>
+        <v>0.1776988041326664</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2693036406190447</v>
+        <v>0.1776988758725165</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2693035688791945</v>
+        <v>0.1776988041326664</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2693036725034225</v>
+        <v>0.1776989077568944</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2693037681565562</v>
+        <v>0.1776990034100281</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2693037043878003</v>
+        <v>0.1776989396412722</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.269303664532328</v>
+        <v>0.1776988997857999</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2693036406190447</v>
+        <v>0.1776988758725165</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2693033935151166</v>
+        <v>0.1776986287685884</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2693033138041718</v>
+        <v>0.1776985490576436</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2693033616307385</v>
+        <v>0.1776985968842104</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2693034811971555</v>
+        <v>0.1776987164506274</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2693034652549666</v>
+        <v>0.1776987005084385</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2693034811971555</v>
+        <v>0.1776987164506274</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2693034652549666</v>
+        <v>0.1776987005084385</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2693035210526278</v>
+        <v>0.1776987563060997</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2693035210526278</v>
+        <v>0.1776987563060997</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2693035210526278</v>
+        <v>0.1776987563060997</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2693036725034225</v>
+        <v>0.1776989077568944</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.269303887722973</v>
+        <v>0.1776991229764449</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.269303800040934</v>
+        <v>0.1776990352944059</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2693037522143673</v>
+        <v>0.1776989874678392</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.269303800040934</v>
+        <v>0.1776990352944059</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2693036167057613</v>
+        <v>0.1776988519592332</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2693036246768558</v>
+        <v>0.1776988599303276</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2693036326479502</v>
+        <v>0.1776988679014221</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2693036406190447</v>
+        <v>0.1776988758725165</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2693036406190447</v>
+        <v>0.1776988758725165</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2693036804745169</v>
+        <v>0.1776989157279888</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2693037442432728</v>
+        <v>0.1776989794967447</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2693038558385952</v>
+        <v>0.1776990910920671</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2693039036651619</v>
+        <v>0.1776991389186338</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2693038638096896</v>
+        <v>0.1776990990631615</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2693037920698396</v>
+        <v>0.1776990273233114</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2693039116362564</v>
+        <v>0.1776991468897283</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2693037522143673</v>
+        <v>0.1776989874678392</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2693035210526278</v>
+        <v>0.1776987563060997</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2693034732260611</v>
+        <v>0.177698708479533</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2693035051104389</v>
+        <v>0.1776987403639108</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2693035688791945</v>
+        <v>0.1776988041326664</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2693035688791945</v>
+        <v>0.1776988041326664</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.26930348916825</v>
+        <v>0.1776987244217219</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2693033696018329</v>
+        <v>0.1776986048553048</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2693033297463607</v>
+        <v>0.1776985649998325</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2693034732260611</v>
+        <v>0.177698708479533</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2693036087346669</v>
+        <v>0.1776988439881387</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2693035927924779</v>
+        <v>0.1776988280459498</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2693035688791945</v>
+        <v>0.1776988041326664</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2693035290237223</v>
+        <v>0.1776987642771942</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2693034253994944</v>
+        <v>0.1776986606529662</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2693033058330773</v>
+        <v>0.1776985410865492</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2693034253994944</v>
+        <v>0.1776986606529662</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2693034732260611</v>
+        <v>0.177698708479533</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2693035688791945</v>
+        <v>0.1776988041326664</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2693034493127777</v>
+        <v>0.1776986845662496</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2693034572838722</v>
+        <v>0.177698692537344</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_1_000001.xlsx
+++ b/out/Attention-Mamba1_repeat_1_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.5195375025212517</v>
+        <v>0.3105400017288584</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.5195375025212517</v>
+        <v>0.3105400017288584</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.5195375025212517</v>
+        <v>0.3105400017288584</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.5195375025212517</v>
+        <v>0.3105400017288584</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.5195375025212517</v>
+        <v>0.3105400017288584</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.5195375025212517</v>
+        <v>0.3105400017288584</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.5195375025212517</v>
+        <v>0.3105400017288584</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC43" t="n">
-        <v>-9.342816364043393e-05</v>
+        <v>-0.0001090284957240801</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.04022734760312981</v>
+        <v>0.04694439765966426</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.08056226633211667</v>
+        <v>0.09401429247585638</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1554195181548552</v>
+        <v>0.1813710348570751</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-0.899639998847428</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.3512782694338442</v>
+        <v>0.4099334561422202</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.04780842403324903</v>
+        <v>0.05579074703577673</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-9.227858435864231</v>
+        <v>-1.909819999423714</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2912771945012859</v>
+        <v>0.3399136772441312</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.009700684866417434</v>
+        <v>0.01132056414588691</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-9.227858435864231</v>
+        <v>-2.92</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2627953484839797</v>
+        <v>0.3066757595844821</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.008400144827556133</v>
+        <v>0.009804104708888126</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-9.227858435864231</v>
+        <v>-1.909819999423714</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2698856671275217</v>
+        <v>0.3149508967804353</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.004104104061585137</v>
+        <v>0.004790121434728823</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.0804624974787482</v>
+        <v>-0.899639998847428</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.2696850453942199</v>
+        <v>0.3147176185436766</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.001956083678599633</v>
+        <v>0.002283487768042161</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2694887422620926</v>
+        <v>0.3144893825626916</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0008122505780637044</v>
+        <v>0.0009486445778086686</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.5195375025212517</v>
+        <v>0.3105400017288584</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.2691542393066245</v>
+        <v>0.3140998876289607</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0005614068736791735</v>
+        <v>0.0006555507954623603</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.5195375025212517</v>
+        <v>0.3105400017288584</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.2694640624969266</v>
+        <v>0.3144622535990542</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0002314533376848248</v>
+        <v>0.0002707548461283515</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.5195375025212517</v>
+        <v>0.3105400017288584</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.2693649465762211</v>
+        <v>0.3143473668951611</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001172754048326176</v>
+        <v>0.0001379887247769408</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.5195375025212517</v>
+        <v>0.3105400017288584</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2693684664920014</v>
+        <v>0.3143523260244792</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>4.328749595342138e-05</v>
+        <v>5.116045725017487e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.5195375025212517</v>
+        <v>0.3105400017288584</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.2693369532375331</v>
+        <v>0.314316346477082</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>2.134113002145089e-05</v>
+        <v>2.5922196112138e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.5195375025212517</v>
+        <v>0.3105400017288584</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.2693362941468426</v>
+        <v>0.3143164423271408</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>7.987449840330433e-06</v>
+        <v>1.024613676908355e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.5195375025212517</v>
+        <v>0.3105400017288584</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.269330898129083</v>
+        <v>0.3143109774367274</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>8.610817715762575e-07</v>
+        <v>1.926733002771942e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.3105400017288584</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.2693251511735464</v>
+        <v>0.3143051004682528</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-2.232968880383854e-06</v>
+        <v>-1.771797027114496e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.2693192833855918</v>
+        <v>0.3142990880489724</v>
       </c>
     </row>
     <row r="60">
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.2693139931434903</v>
+        <v>0.3142937499803042</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.68213567138761e-06</v>
+        <v>-4.36427134277522e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2693087052046398</v>
+        <v>0.3142883654088704</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2693034333705888</v>
+        <v>0.3142830935748194</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.2693034732260611</v>
+        <v>0.3142831334302917</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2693035130815334</v>
+        <v>0.3142831732857639</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2693035051104389</v>
+        <v>0.3142831653146695</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.269303664532328</v>
+        <v>0.3142833247365586</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2693035688791945</v>
+        <v>0.3142832290834252</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2693039196073508</v>
+        <v>0.3142835798115814</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2693036725034225</v>
+        <v>0.3142833327076531</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2693036326479502</v>
+        <v>0.3142832928521808</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2693035688791945</v>
+        <v>0.3142832290834252</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2693036406190447</v>
+        <v>0.3142833008232752</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2693035688791945</v>
+        <v>0.3142832290834252</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2693036725034225</v>
+        <v>0.3142833327076531</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2693037681565562</v>
+        <v>0.3142834283607868</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2693037043878003</v>
+        <v>0.3142833645920309</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.269303664532328</v>
+        <v>0.3142833247365586</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2693036406190447</v>
+        <v>0.3142833008232752</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2693033935151166</v>
+        <v>0.3142830537193471</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2693033138041718</v>
+        <v>0.3142829740084023</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2693033616307385</v>
+        <v>0.314283021834969</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2693034811971555</v>
+        <v>0.3142831414013861</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2693034652549666</v>
+        <v>0.3142831254591972</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2693034811971555</v>
+        <v>0.3142831414013861</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2693034652549666</v>
+        <v>0.3142831254591972</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2693035210526278</v>
+        <v>0.3142831812568584</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2693035210526278</v>
+        <v>0.3142831812568584</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2693035210526278</v>
+        <v>0.3142831812568584</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2693036725034225</v>
+        <v>0.3142833327076531</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.269303887722973</v>
+        <v>0.3142835479272036</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.269303800040934</v>
+        <v>0.3142834602451646</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2693037522143673</v>
+        <v>0.3142834124185979</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.269303800040934</v>
+        <v>0.3142834602451646</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2693036167057613</v>
+        <v>0.3142832769099919</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2693036246768558</v>
+        <v>0.3142832848810863</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2693036326479502</v>
+        <v>0.3142832928521808</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2693036406190447</v>
+        <v>0.3142833008232752</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2693036406190447</v>
+        <v>0.3142833008232752</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2693036804745169</v>
+        <v>0.3142833406787475</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2693037442432728</v>
+        <v>0.3142834044475034</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2693038558385952</v>
+        <v>0.3142835160428258</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2693039036651619</v>
+        <v>0.3142835638693925</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2693038638096896</v>
+        <v>0.3142835240139202</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2693037920698396</v>
+        <v>0.3142834522740701</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2693039116362564</v>
+        <v>0.3142835718404869</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2693037522143673</v>
+        <v>0.3142834124185979</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2693035210526278</v>
+        <v>0.3142831812568584</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2693034732260611</v>
+        <v>0.3142831334302917</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2693035051104389</v>
+        <v>0.3142831653146695</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2693035688791945</v>
+        <v>0.3142832290834252</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2693035688791945</v>
+        <v>0.3142832290834252</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.26930348916825</v>
+        <v>0.3142831493724806</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2693033696018329</v>
+        <v>0.3142830298060635</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2693033297463607</v>
+        <v>0.3142829899505912</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2693034732260611</v>
+        <v>0.3142831334302917</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2693036087346669</v>
+        <v>0.3142832689388974</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2693035927924779</v>
+        <v>0.3142832529967085</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2693035688791945</v>
+        <v>0.3142832290834252</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2693035290237223</v>
+        <v>0.3142831892279528</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2693034253994944</v>
+        <v>0.3142830856037249</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2693033058330773</v>
+        <v>0.3142829660373079</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2693034253994944</v>
+        <v>0.3142830856037249</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2693034732260611</v>
+        <v>0.3142831334302917</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2693035688791945</v>
+        <v>0.3142832290834252</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2693034493127777</v>
+        <v>0.3142831095170083</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.0804624974787482</v>
+        <v>0.1105400017288584</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2693034572838722</v>
+        <v>0.3142831174881028</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_1_000001.xlsx
+++ b/out/Attention-Mamba1_repeat_1_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.004348837770521641</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.16</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.005835154093801975</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.09</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.00381088349968195</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.3105400017288584</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.003543254919350147</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.3105400017288584</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.004599682055413723</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.3105400017288584</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.006218382157385349</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.3105400017288584</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.003972521983087063</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.3105400017288584</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.004246908240020275</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.3105400017288584</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.004845709539949894</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.3105400017288584</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.003375533036887646</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.004223321564495564</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.00390318688005209</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.005127561278641224</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.006453470326960087</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.006815494038164616</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.006229530088603497</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.004358571954071522</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.004681522957980633</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.004402610473334789</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.003236033953726292</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.003322715871036053</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.004087044857442379</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.004993426613509655</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.005624952726066113</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.004508386366069317</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.004587368108332157</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.16</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.004466420970857143</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.003972741775214672</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.16</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.004779147915542126</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.007154184393584728</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.004625090397894382</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.005559324286878109</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.004916946403682232</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.16</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.004394960589706898</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.004321112297475338</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.004652419127523899</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.004892335273325443</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.16</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.005111505277454853</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.007555733434855938</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.0083684166893363</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01267170626670122</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.01270028855651617</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0001090284957240801</v>
+        <v>-0.0001816752822221024</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.04694439765966426</v>
+        <v>0.07822410178061202</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.02166706509888172</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.09401429247585638</v>
+        <v>0.1566569630070983</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1813710348570751</v>
+        <v>0.3022210742498265</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.01395306643098593</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.899639998847428</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4099334561422202</v>
+        <v>0.6830750487817598</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.05579074703577673</v>
+        <v>0.09296489660347235</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.005658769048750401</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.909819999423714</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3399136772441312</v>
+        <v>0.5664011813620098</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.01132056414588691</v>
+        <v>0.01886306248949166</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.001356708817183971</v>
       </c>
       <c r="JB47" t="n">
-        <v>-2.92</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3066757595844821</v>
+        <v>0.5110173888417329</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.009804104708888126</v>
+        <v>0.01633660823303623</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.0008279075846076012</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.909819999423714</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3149508967804353</v>
+        <v>0.5248062758631562</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.004790121434728823</v>
+        <v>0.007985702361668543</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.002317427657544613</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.899639998847428</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.3147176185436766</v>
+        <v>0.524420894243811</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.002283487768042161</v>
+        <v>0.003808255384588791</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.001451288349926472</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.3144893825626916</v>
+        <v>0.5240439424238605</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0009486445778086686</v>
+        <v>0.001583850919478074</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.002144894562661648</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.3105400017288584</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.3140998876289607</v>
+        <v>0.5233983419913631</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0006555507954623603</v>
+        <v>0.001096175216267276</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.001278459094464779</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.3105400017288584</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.3144622535990542</v>
+        <v>0.5240054028804111</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0002707548461283515</v>
+        <v>0.0004543766478726977</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.005097425542771816</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.3105400017288584</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.3143473668951611</v>
+        <v>0.5238174288811471</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001379887247769408</v>
+        <v>0.0002335372651652704</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.004044803790748119</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.3105400017288584</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.3143523260244792</v>
+        <v>0.5238290030499527</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>5.116045725017487e-05</v>
+        <v>8.842580738814138e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.0008140234276652336</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.3105400017288584</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.314316346477082</v>
+        <v>0.5237725621866074</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>2.5922196112138e-05</v>
+        <v>4.596436025889411e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.001328646205365658</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.3105400017288584</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.3143164423271408</v>
+        <v>0.5237760087290115</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.024613676908355e-05</v>
+        <v>2.041022794847258e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.0004116268828511238</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.3105400017288584</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.3143109774367274</v>
+        <v>0.5237702339116556</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.926733002771942e-06</v>
+        <v>6.722163543152517e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.00106485839933157</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.3105400017288584</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.3143051004682528</v>
+        <v>0.5237637718849604</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-1.771797027114496e-06</v>
+        <v>7.289038596293463e-08</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.00115704070776701</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.3142990880489724</v>
+        <v>0.5237571092005268</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-3.759791964848896e-06</v>
+        <v>-2.519583929697793e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.001433239318430424</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3142937499803042</v>
+        <v>0.5237515287163241</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.36427134277522e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.002173702232539654</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3142883654088704</v>
+        <v>0.5237459518591734</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.001898183487355709</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3142830935748194</v>
+        <v>0.5237405445165164</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>-4.777674021158921e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.002742809243500233</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3142831334302917</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.001396750099956989</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3142831732857639</v>
+        <v>0.5237356632182673</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.003076191060245037</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3142831653146695</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.001688527874648571</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3142833247365586</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.004938387311995029</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3142832290834252</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.001615052111446857</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3142835798115814</v>
+        <v>0.5237360697440847</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.001502596773207188</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3142833327076531</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.00225504394620657</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3142832928521808</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.001168203540146351</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3142832290834252</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.001391815952956676</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3142833008232752</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.001914049498736858</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3142832290834252</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.01548982225358486</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3142833327076531</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.00161649938672781</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3142834283607868</v>
+        <v>0.52373591829329</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.0008117137476801872</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3142833645920309</v>
+        <v>0.5237358545245342</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.00113349687308073</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3142833247365586</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.002319457940757275</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3142833008232752</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.001546227373182774</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3142830537193471</v>
+        <v>0.5237355436518504</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.00142271164804697</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3142829740084023</v>
+        <v>0.5237354639409056</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.001451962627470493</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.314283021834969</v>
+        <v>0.5237355117674724</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.0007841968908905983</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3142831414013861</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.001525170169770718</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3142831254591972</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.001253669150173664</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3142831414013861</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.00161751639097929</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3142831254591972</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.001157556660473347</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3142831812568584</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.0008596880361437798</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3142831812568584</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.003641487099230289</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3142831812568584</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.0008221445605158806</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.16</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3142833327076531</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.004546088166534901</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3142835479272036</v>
+        <v>0.5237360378597069</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.0002795299515128136</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3142834602451646</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.001263578422367573</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3142834124185979</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.001266825012862682</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3142834602451646</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.0007995879277586937</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3142832769099919</v>
+        <v>0.5237357668424952</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.0009477837011218071</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3142832848810863</v>
+        <v>0.5237357748135897</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.001280111260712147</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3142832928521808</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.0004659174010157585</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3142833008232752</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.0008716313168406487</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3142833008232752</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.003153999336063862</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3142833406787475</v>
+        <v>0.5237358306112508</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.001507922075688839</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3142834044475034</v>
+        <v>0.5237358943800067</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.001739361323416233</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3142835160428258</v>
+        <v>0.5237360059753291</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.0006521204486489296</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3142835638693925</v>
+        <v>0.5237360538018958</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.001479160971939564</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.16</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3142835240139202</v>
+        <v>0.5237360139464236</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.001629936508834362</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3142834522740701</v>
+        <v>0.5237359422065735</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.001662231050431728</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3142835718404869</v>
+        <v>0.5237360617729903</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.002613336779177189</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3142834124185979</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.001468664966523647</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3142831812568584</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.001733968965709209</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3142831334302917</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.00115275289863348</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.16</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3142831653146695</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.001492924056947231</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3142832290834252</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.0008125463500618935</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3142832290834252</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.001175428740680218</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3142831493724806</v>
+        <v>0.5237356393049839</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.00154546182602644</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3142830298060635</v>
+        <v>0.5237355197385668</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.001515249721705914</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3142829899505912</v>
+        <v>0.5237354798830945</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.001640019007027149</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3142831334302917</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.001016116701066494</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3142832689388974</v>
+        <v>0.5237357588714008</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.0007386384531855583</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3142832529967085</v>
+        <v>0.5237357429292118</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.001166592352092266</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3142832290834252</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.001345832832157612</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3142831892279528</v>
+        <v>0.5237356791604562</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.002484860830008984</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3142830856037249</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.003086422570049763</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3142829660373079</v>
+        <v>0.5237354559698112</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.001439732499420643</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3142830856037249</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.001945647411048412</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3142831334302917</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.001056361012160778</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3142832290834252</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.001647344790399075</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.1105400017288584</v>
+        <v>0.2299999999999999</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3142831095170083</v>
+        <v>0.5237355994495116</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.002777674235403538</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.1105400017288584</v>
+        <v>-0.4400000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3142831174881028</v>
+        <v>0.5237356074206061</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_1_000001.xlsx
+++ b/out/Attention-Mamba1_repeat_1_000001.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.004348837770521641</v>
+        <v>0.004348811693489552</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.16</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.005835154093801975</v>
+        <v>0.005835180170834064</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.09</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.00381088349968195</v>
+        <v>0.003810849972069263</v>
       </c>
       <c r="JB4" t="n">
         <v>0.5799999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.003543254919350147</v>
+        <v>0.003543234430253506</v>
       </c>
       <c r="JB5" t="n">
         <v>0.7199999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.004599682055413723</v>
+        <v>0.004599676467478275</v>
       </c>
       <c r="JB6" t="n">
         <v>0.5799999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.006218382157385349</v>
+        <v>0.006218361668288708</v>
       </c>
       <c r="JB7" t="n">
         <v>0.7199999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.003972521983087063</v>
+        <v>0.003972488455474377</v>
       </c>
       <c r="JB8" t="n">
         <v>0.8599999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.004246908240020275</v>
+        <v>0.004246885888278484</v>
       </c>
       <c r="JB9" t="n">
         <v>0.7199999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.004845709539949894</v>
+        <v>0.004845716990530491</v>
       </c>
       <c r="JB10" t="n">
         <v>0.5799999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.004223321564495564</v>
+        <v>0.00422330666333437</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.02000000000000007</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.00390318688005209</v>
+        <v>0.003903216682374477</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.02000000000000007</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.005127561278641224</v>
+        <v>0.005127527751028538</v>
       </c>
       <c r="JB14" t="n">
         <v>0.1199999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.006453470326960087</v>
+        <v>0.00645346287637949</v>
       </c>
       <c r="JB15" t="n">
         <v>0.8599999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.006815494038164616</v>
+        <v>0.006815505214035511</v>
       </c>
       <c r="JB16" t="n">
         <v>0.7199999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.006229530088603497</v>
+        <v>0.006229558028280735</v>
       </c>
       <c r="JB17" t="n">
         <v>0.5799999999999998</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.004358571954071522</v>
+        <v>0.004358616657555103</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.3</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.004681522957980633</v>
+        <v>0.004681500606238842</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.5799999999999998</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.004402610473334789</v>
+        <v>0.0044025843963027</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.8599999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.003236033953726292</v>
+        <v>0.003236041404306889</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.8599999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.003322715871036053</v>
+        <v>0.003322684206068516</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.7199999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.004087044857442379</v>
+        <v>0.004087033681571484</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.4399999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.004993426613509655</v>
+        <v>0.004993374459445477</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.3</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.005624952726066113</v>
+        <v>0.005624941550195217</v>
       </c>
       <c r="JB25" t="n">
         <v>0.4399999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.004508386366069317</v>
+        <v>0.004508395679295063</v>
       </c>
       <c r="JB26" t="n">
         <v>0.4399999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.004587368108332157</v>
+        <v>0.004587375558912754</v>
       </c>
       <c r="JB27" t="n">
         <v>0.16</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.004466420970857143</v>
+        <v>0.004466407932341099</v>
       </c>
       <c r="JB28" t="n">
         <v>0.02000000000000007</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.003972741775214672</v>
+        <v>0.003972764126956463</v>
       </c>
       <c r="JB29" t="n">
         <v>0.16</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.004779147915542126</v>
+        <v>0.004779155366122723</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.4399999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.004625090397894382</v>
+        <v>0.004625084809958935</v>
       </c>
       <c r="JB32" t="n">
         <v>0.5799999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.005559324286878109</v>
+        <v>0.005559320561587811</v>
       </c>
       <c r="JB33" t="n">
         <v>0.4399999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.004916946403682232</v>
+        <v>0.004916938953101635</v>
       </c>
       <c r="JB34" t="n">
         <v>0.16</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.004394960589706898</v>
+        <v>0.00439495500177145</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.4399999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.004321112297475338</v>
+        <v>0.004321143962442875</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.5799999999999998</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.004652419127523899</v>
+        <v>0.004652398638427258</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.4399999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.004892335273325443</v>
+        <v>0.004892311058938503</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.16</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.005111505277454853</v>
+        <v>0.005111497826874256</v>
       </c>
       <c r="JB39" t="n">
         <v>0.7199999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.007555733434855938</v>
+        <v>0.007555748336017132</v>
       </c>
       <c r="JB40" t="n">
         <v>0.8599999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.0083684166893363</v>
+        <v>0.008368452079594135</v>
       </c>
       <c r="JB41" t="n">
         <v>0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.01267170626670122</v>
+        <v>0.01267172675579786</v>
       </c>
       <c r="JB42" t="n">
         <v>0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.01270028855651617</v>
+        <v>0.01270030345767736</v>
       </c>
       <c r="JB43" t="n">
         <v>0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.02166706509888172</v>
+        <v>0.02166702598333359</v>
       </c>
       <c r="JB44" t="n">
         <v>0.7199999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.01395306643098593</v>
+        <v>0.01395306270569563</v>
       </c>
       <c r="JB45" t="n">
         <v>0.4399999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.005658769048750401</v>
+        <v>-0.005658750422298908</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.4399999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.001356708817183971</v>
+        <v>-0.001356723718345165</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.7199999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.0008279075846076012</v>
+        <v>-0.0008278479799628258</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.002317427657544613</v>
+        <v>0.002317438833415508</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.001451288349926472</v>
+        <v>0.001451301388442516</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.002144894562661648</v>
+        <v>0.002144900150597095</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
         <v>0.5233983419913631</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.001278459094464779</v>
+        <v>0.001278466545045376</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
         <v>0.5240054028804111</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.005097425542771816</v>
+        <v>0.005097429268062115</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
         <v>0.5238174288811471</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.004044803790748119</v>
+        <v>0.004044818691909313</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
         <v>0.5238290030499527</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.0008140234276652336</v>
+        <v>0.0008140159770846367</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
         <v>0.5237725621866074</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.001328646205365658</v>
+        <v>0.001328631304204464</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.0004116268828511238</v>
+        <v>0.00041163619607687</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.00106485839933157</v>
+        <v>0.001064862124621868</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.00115704070776701</v>
+        <v>0.001157048158347607</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.001433239318430424</v>
+        <v>0.001433244906365871</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.002173702232539654</v>
+        <v>0.002173681743443012</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.001898183487355709</v>
+        <v>0.001898207701742649</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.002742809243500233</v>
+        <v>0.002742811106145382</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.001396750099956989</v>
+        <v>0.00139674823731184</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.003076191060245037</v>
+        <v>0.003076161257922649</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.1199999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.001688527874648571</v>
+        <v>0.001688511110842228</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.1199999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.004938387311995029</v>
+        <v>0.004938381724059582</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.1199999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.001615052111446857</v>
+        <v>0.001615035347640514</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.1199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.001502596773207188</v>
+        <v>0.001502587459981441</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.1199999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.00225504394620657</v>
+        <v>0.002255045808851719</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.3999999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.001168203540146351</v>
+        <v>0.001168222166597843</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.001391815952956676</v>
+        <v>0.001391827128827572</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.7199999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.001914049498736858</v>
+        <v>0.00191404577344656</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.7199999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.00161649938672781</v>
+        <v>0.001616504974663258</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.1199999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.0008117137476801872</v>
+        <v>0.0008117156103253365</v>
       </c>
       <c r="JB76" t="n">
         <v>0.02000000000000007</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.00113349687308073</v>
+        <v>0.001133506186306477</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.2599999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.002319457940757275</v>
+        <v>0.002319470979273319</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.2599999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.001546227373182774</v>
+        <v>0.001546242274343967</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.8599999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.00142271164804697</v>
+        <v>0.001422750763595104</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.8599999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.001451962627470493</v>
+        <v>0.001451966352760792</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.9999999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.0007841968908905983</v>
+        <v>0.0007842360064387321</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.9999999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.001525170169770718</v>
+        <v>0.001525194384157658</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.9999999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.001253669150173664</v>
+        <v>0.001253695227205753</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.9999999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.00161751639097929</v>
+        <v>0.001617527566850185</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.9999999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.001157556660473347</v>
+        <v>0.00115757342427969</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.1199999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.0008596880361437798</v>
+        <v>0.0008596805855631828</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.1199999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.003641487099230289</v>
+        <v>0.003641475923359394</v>
       </c>
       <c r="JB88" t="n">
         <v>0.1600000000000001</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.0008221445605158806</v>
+        <v>0.0008221426978707314</v>
       </c>
       <c r="JB89" t="n">
         <v>0.16</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.004546088166534901</v>
+        <v>0.004546063952147961</v>
       </c>
       <c r="JB90" t="n">
         <v>0.1600000000000001</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.0002795299515128136</v>
+        <v>0.0002795374020934105</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.1199999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.001263578422367573</v>
+        <v>0.001263587735593319</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.1199999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.0007995879277586937</v>
+        <v>0.0007995972409844398</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.9999999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.001280111260712147</v>
+        <v>0.001280100084841251</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.9999999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.0004659174010157585</v>
+        <v>0.0004659323021769524</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.7199999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.0008716313168406487</v>
+        <v>0.000871625728905201</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.7199999999999999</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.003153999336063862</v>
+        <v>0.003153995610773563</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC99" t="n">
         <v>0.5237358306112508</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.001507922075688839</v>
+        <v>0.001507912762463093</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0.5237358943800067</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.001739361323416233</v>
+        <v>0.001739366911351681</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC101" t="n">
         <v>0.5237360059753291</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.0006521204486489296</v>
+        <v>0.0006521223112940788</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC102" t="n">
         <v>0.5237360538018958</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.001479160971939564</v>
+        <v>0.00147914607077837</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.16</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
         <v>0.5237360139464236</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.001629936508834362</v>
+        <v>0.001629943959414959</v>
       </c>
       <c r="JB104" t="n">
         <v>0.3</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.001662231050431728</v>
+        <v>0.001662223599851131</v>
       </c>
       <c r="JB105" t="n">
         <v>0.4399999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.002613336779177189</v>
+        <v>0.002613340504467487</v>
       </c>
       <c r="JB106" t="n">
         <v>0.7199999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.001468664966523647</v>
+        <v>0.001468689180910587</v>
       </c>
       <c r="JB107" t="n">
         <v>0.5799999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.001733968965709209</v>
+        <v>0.001733974553644657</v>
       </c>
       <c r="JB108" t="n">
         <v>0.4399999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.00115275289863348</v>
+        <v>0.001152767799794674</v>
       </c>
       <c r="JB109" t="n">
         <v>0.16</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.001492924056947231</v>
+        <v>0.001492929644882679</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.5799999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.0008125463500618935</v>
+        <v>0.0008125444874167442</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.7199999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.001175428740680218</v>
+        <v>0.00117544736713171</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.5799999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.00154546182602644</v>
+        <v>0.001545482315123081</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.5799999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.001515249721705914</v>
+        <v>0.001515242271125317</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.5799999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.001640019007027149</v>
+        <v>0.001640032045543194</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.5799999999999998</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.001016116701066494</v>
+        <v>0.001016124151647091</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.7199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.0007386384531855583</v>
+        <v>0.0007386272773146629</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.7199999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.001166592352092266</v>
+        <v>0.001166575588285923</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.5799999999999998</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.001345832832157612</v>
+        <v>0.001345851458609104</v>
       </c>
       <c r="JB119" t="n">
         <v>0.3</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.002484860830008984</v>
+        <v>0.002484858967363834</v>
       </c>
       <c r="JB120" t="n">
         <v>0.4399999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.003086422570049763</v>
+        <v>0.003086411394178867</v>
       </c>
       <c r="JB121" t="n">
         <v>0.7199999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.001439732499420643</v>
+        <v>0.001439721323549747</v>
       </c>
       <c r="JB122" t="n">
         <v>0.5799999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.001945647411048412</v>
+        <v>0.001945630647242069</v>
       </c>
       <c r="JB123" t="n">
         <v>0.4399999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.001056361012160778</v>
+        <v>0.001056362874805927</v>
       </c>
       <c r="JB124" t="n">
         <v>0.3</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.001647344790399075</v>
+        <v>0.001647328026592731</v>
       </c>
       <c r="JB125" t="n">
         <v>0.2299999999999999</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.002777674235403538</v>
+        <v>0.002777659334242344</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.4400000000000001</v>
